--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/CONNECTICUT_2020.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/CONNECTICUT_2020.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D508"/>
+  <dimension ref="A1:D502"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -457,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C7">
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -483,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bejucal de Ocampo</t>
+          <t>Bejucal De Ocampo</t>
         </is>
       </c>
       <c r="C9">
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Cintalapa</t>
@@ -548,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C14">
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>El Bosque</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -613,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -626,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -639,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Jiquipilas</t>
@@ -652,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -665,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -678,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -691,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -704,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -717,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C27">
@@ -730,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -739,10 +859,15 @@
         <v>16</v>
       </c>
       <c r="D28">
-        <v>0.009925558312655087</v>
+        <v>0.009925558312655089</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -756,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Teopisca</t>
@@ -769,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -782,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -795,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -808,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Total</t>
@@ -839,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Total</t>
@@ -901,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -914,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -929,7 +1099,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -945,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -958,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C44">
@@ -971,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -984,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -997,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1010,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1023,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1036,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1049,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1080,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1095,12 +1315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C54">
@@ -1111,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Apaxco</t>
@@ -1124,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Atlautla</t>
@@ -1137,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1150,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Chicoloapan</t>
@@ -1163,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1176,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -1189,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C61">
@@ -1202,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -1215,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1228,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -1241,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C65">
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1267,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C67">
@@ -1280,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -1293,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1306,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Texcaltitlán</t>
@@ -1319,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C71">
@@ -1332,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -1345,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1358,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Villa Guerero</t>
@@ -1371,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -1384,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Zumpango</t>
@@ -1397,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1412,12 +1747,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C78">
@@ -1428,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1441,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -1454,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1467,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>León</t>
@@ -1480,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -1493,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -1519,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Tarandacuao</t>
@@ -1532,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -1558,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -1596,7 +1986,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C91">
@@ -1607,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1620,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Alcozauca de Guerero</t>
+          <t>Alcozauca De Guerero</t>
         </is>
       </c>
       <c r="C93">
@@ -1633,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -1646,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -1659,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C96">
@@ -1672,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1685,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C98">
@@ -1698,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Coahuayutla de José María Izazaga</t>
+          <t>Coahuayutla De José María Izazaga</t>
         </is>
       </c>
       <c r="C99">
@@ -1711,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -1724,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Copala</t>
@@ -1737,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -1750,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C103">
@@ -1763,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -1776,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -1789,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Huamuxtitlán</t>
@@ -1802,9 +2267,14 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C107">
@@ -1815,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -1828,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C109">
@@ -1841,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -1854,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -1867,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -1880,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -1893,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -1906,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -1919,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -1932,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -1945,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C118">
@@ -1958,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -1971,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tixtla de Guerero</t>
+          <t>Tixtla De Guerero</t>
         </is>
       </c>
       <c r="C120">
@@ -1984,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C121">
@@ -1997,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -2010,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Xochihuehuetlán</t>
@@ -2023,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Zapotitlán Tablas</t>
@@ -2036,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2067,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Almoloya</t>
@@ -2080,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Apan</t>
@@ -2093,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Chapantongo</t>
@@ -2106,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -2119,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -2132,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -2145,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Huazalingo</t>
@@ -2158,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -2171,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -2184,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -2197,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mixquiahuala de Juárez</t>
+          <t>Mixquiahuala De Juárez</t>
         </is>
       </c>
       <c r="C137">
@@ -2210,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Nicolás Flores</t>
@@ -2223,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C139">
@@ -2236,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Tasquillo</t>
@@ -2249,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -2262,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Tepeapulco</t>
@@ -2275,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Tianguistengo</t>
@@ -2288,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Tlahuiltepa</t>
@@ -2301,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Zempoala</t>
@@ -2314,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -2327,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2347,7 +3012,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C148">
@@ -2358,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -2371,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -2384,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C151">
@@ -2397,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Etzatlán</t>
@@ -2410,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2423,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ixtlahuacán del Río</t>
+          <t>Ixtlahuacán Del Río</t>
         </is>
       </c>
       <c r="C154">
@@ -2436,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Jilotlán de los Dolores</t>
+          <t>Jilotlán De Los Dolores</t>
         </is>
       </c>
       <c r="C155">
@@ -2449,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -2462,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -2475,9 +3185,14 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C158">
@@ -2488,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Mazamitla</t>
@@ -2501,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Mixtlán</t>
@@ -2514,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -2527,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -2540,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -2553,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>San Juanito de Escobedo</t>
+          <t>San Juanito De Escobedo</t>
         </is>
       </c>
       <c r="C164">
@@ -2566,9 +3311,14 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C165">
@@ -2579,9 +3329,14 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Teocuitatlán de Corona</t>
+          <t>Teocuitatlán De Corona</t>
         </is>
       </c>
       <c r="C166">
@@ -2592,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C167">
@@ -2605,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -2618,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Tonila</t>
@@ -2631,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2644,9 +3419,14 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Valle de Juárez</t>
+          <t>Valle De Juárez</t>
         </is>
       </c>
       <c r="C171">
@@ -2657,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2670,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Zapotiltic</t>
@@ -2683,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2714,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Aguililla</t>
@@ -2727,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -2740,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -2753,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Cotija</t>
@@ -2766,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Huaniqueo</t>
@@ -2779,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -2792,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Jiquilpan</t>
@@ -2805,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -2818,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -2831,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2844,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -2857,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -2870,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -2883,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Madero</t>
@@ -2896,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Marcos Castellanos</t>
@@ -2909,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2922,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -2935,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -2948,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -2961,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Susupuato</t>
@@ -2974,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -2987,9 +3887,14 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C197">
@@ -3000,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Tocumbo</t>
@@ -3013,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -3026,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -3039,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -3052,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -3065,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3096,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Atlatlahucan</t>
@@ -3109,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Ayala</t>
@@ -3122,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -3135,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -3148,9 +4103,14 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Jonacatepec de Leandro Valle</t>
+          <t>Jonacatepec De Leandro Valle</t>
         </is>
       </c>
       <c r="C209">
@@ -3161,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -3174,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Temoac</t>
@@ -3187,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -3200,9 +4175,14 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C213">
@@ -3213,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -3226,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -3239,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Yecapixtla</t>
@@ -3252,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Zacualpan de Amilpas</t>
+          <t>Zacualpan De Amilpas</t>
         </is>
       </c>
       <c r="C217">
@@ -3265,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3296,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Huajicori</t>
@@ -3309,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3340,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3360,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C224">
@@ -3371,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Asunción Ocotlán</t>
@@ -3384,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Calihualá</t>
@@ -3397,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -3410,9 +4445,14 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Fresnillo de Trujano</t>
+          <t>Fresnillo De Trujano</t>
         </is>
       </c>
       <c r="C228">
@@ -3423,9 +4463,14 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C229">
@@ -3436,9 +4481,14 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C230">
@@ -3449,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Magdalena Tequisistlán</t>
@@ -3462,9 +4517,14 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Nejapa de Madero</t>
+          <t>Nejapa De Madero</t>
         </is>
       </c>
       <c r="C232">
@@ -3475,9 +4535,14 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C233">
@@ -3488,9 +4553,14 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C234">
@@ -3501,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerero</t>
+          <t>Putla Villa De Guerero</t>
         </is>
       </c>
       <c r="C235">
@@ -3514,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -3527,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>San Agustín Chayuco</t>
@@ -3540,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>San Agustín Yatareni</t>
@@ -3553,9 +4643,14 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>San Antonino el Alto</t>
+          <t>San Antonino El Alto</t>
         </is>
       </c>
       <c r="C239">
@@ -3566,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>San Francisco Cajonos</t>
@@ -3579,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>San Francisco Ozolotepec</t>
@@ -3592,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>San Ildefonso Villa Alta</t>
@@ -3605,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>San Jacinto Tlacotepec</t>
@@ -3618,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>San José Lachiguiri</t>
@@ -3631,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>San Juan Bautista Guelache</t>
@@ -3644,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -3657,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>San Juan Cacahuatepec</t>
@@ -3670,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>San Juan Colorado</t>
@@ -3683,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>San Juan Cotzocón</t>
@@ -3696,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>San Juan Juquila Vijanos</t>
@@ -3709,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>San Juan Mazatlán</t>
@@ -3722,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>San Juan Teposcolula</t>
@@ -3735,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>San Juan Ñumí</t>
@@ -3748,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -3761,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>San Mateo Cajonos</t>
@@ -3774,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>San Mateo Etlatongo</t>
@@ -3787,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>San Mateo Piñas</t>
@@ -3800,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>San Mateo Sindihui</t>
@@ -3813,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>San Miguel Amatitlán</t>
@@ -3826,9 +5021,14 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>San Miguel el Grande</t>
+          <t>San Miguel El Grande</t>
         </is>
       </c>
       <c r="C260">
@@ -3839,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>San Miguel Quetzaltepec</t>
@@ -3852,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>San Miguel Soyaltepec</t>
@@ -3865,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>San Pedro Atoyac</t>
@@ -3878,9 +5093,14 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>San Pedro y San Pablo Teposcolula</t>
+          <t>San Pedro Y San Pablo Teposcolula</t>
         </is>
       </c>
       <c r="C264">
@@ -3891,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>San Sebastián Teitipac</t>
@@ -3904,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>San Vicente Coatlán</t>
@@ -3917,9 +5147,14 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Santa Ana del Valle</t>
+          <t>Santa Ana Del Valle</t>
         </is>
       </c>
       <c r="C267">
@@ -3930,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -3943,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Santa Catarina Quiané</t>
@@ -3956,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Santa Cruz Itundujia</t>
@@ -3969,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Santa Cruz Xitla</t>
@@ -3982,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Santa María Huazolotitlán</t>
@@ -3995,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -4008,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Santiago Chazumba</t>
@@ -4021,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -4034,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -4047,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Santiago Matatlán</t>
@@ -4060,9 +5345,14 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Santo Domingo de Morelos</t>
+          <t>Santo Domingo De Morelos</t>
         </is>
       </c>
       <c r="C278">
@@ -4073,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Santo Domingo Teojomulco</t>
@@ -4086,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -4099,9 +5399,14 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Tlalixtac de Cabrera</t>
+          <t>Tlalixtac De Cabrera</t>
         </is>
       </c>
       <c r="C281">
@@ -4112,9 +5417,14 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Totontepec Villa de Morelos</t>
+          <t>Totontepec Villa De Morelos</t>
         </is>
       </c>
       <c r="C282">
@@ -4125,9 +5435,14 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Villa de Zaachila</t>
+          <t>Villa De Zaachila</t>
         </is>
       </c>
       <c r="C283">
@@ -4138,9 +5453,14 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Villa Sola de Vega</t>
+          <t>Villa Sola De Vega</t>
         </is>
       </c>
       <c r="C284">
@@ -4151,9 +5471,14 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C285">
@@ -4164,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4173,7 +5503,7 @@
         <v>149</v>
       </c>
       <c r="D286">
-        <v>0.09243176178660049</v>
+        <v>0.09243176178660048</v>
       </c>
     </row>
     <row r="287">
@@ -4195,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -4208,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Ahuacatlán</t>
@@ -4221,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Ahuazotepec</t>
@@ -4234,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Ahuehuetitla</t>
@@ -4247,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Albino Zertuche</t>
@@ -4260,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Amixtlán</t>
@@ -4273,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Amozoc</t>
@@ -4286,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -4299,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Atzitzihuacán</t>
@@ -4312,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Axutla</t>
@@ -4325,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -4338,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -4351,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -4364,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -4377,9 +5777,14 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Chila de la Sal</t>
+          <t>Chila De La Sal</t>
         </is>
       </c>
       <c r="C302">
@@ -4390,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Chinantla</t>
@@ -4403,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Coatepec</t>
@@ -4416,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -4429,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Coxcatlán</t>
@@ -4442,9 +5867,14 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Cuapiaxtla de Madero</t>
+          <t>Cuapiaxtla De Madero</t>
         </is>
       </c>
       <c r="C307">
@@ -4455,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Cuautinchán</t>
@@ -4468,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Cuautlancingo</t>
@@ -4481,9 +5921,14 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C310">
@@ -4494,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Cuyoaco</t>
@@ -4507,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Epatlán</t>
@@ -4520,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Francisco Z. Mena</t>
@@ -4533,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -4546,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -4559,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Honey</t>
@@ -4572,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -4585,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Huatlatlauca</t>
@@ -4598,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -4611,9 +6101,14 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C320">
@@ -4624,9 +6119,14 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Huehuetlán el Grande</t>
+          <t>Huehuetlán El Grande</t>
         </is>
       </c>
       <c r="C321">
@@ -4637,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -4650,9 +6155,14 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Ixcamilpa de Guerero</t>
+          <t>Ixcamilpa De Guerero</t>
         </is>
       </c>
       <c r="C323">
@@ -4663,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -4676,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Ixtepec</t>
@@ -4689,9 +6209,14 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C326">
@@ -4702,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Jonotla</t>
@@ -4715,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Jopala</t>
@@ -4728,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Juan C. Bonilla</t>
@@ -4741,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -4754,9 +6299,14 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C331">
@@ -4767,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Mixtla</t>
@@ -4780,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Nealtican</t>
@@ -4793,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -4806,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Ocoyucan</t>
@@ -4819,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Oriental</t>
@@ -4832,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Pahuatlán</t>
@@ -4845,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -4858,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -4871,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -4884,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -4897,6 +6497,11 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
           <t>San Felipe Teotlalcingo</t>
@@ -4910,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>San Gabriel Chilac</t>
@@ -4923,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>San Gregorio Atzompa</t>
@@ -4936,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>San Jerónimo Tecuanipan</t>
@@ -4949,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>San Jerónimo Xayacatlán</t>
@@ -4962,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -4975,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>San Martín Totoltepec</t>
@@ -4988,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>San Miguel Xoxtla</t>
@@ -5001,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>San Nicolás Buenos Aires</t>
@@ -5014,9 +6659,14 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>San Nicolás de los Ranchos</t>
+          <t>San Nicolás De Los Ranchos</t>
         </is>
       </c>
       <c r="C351">
@@ -5027,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>San Pablo Anicano</t>
@@ -5040,6 +6695,11 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -5053,6 +6713,11 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
           <t>San Pedro Yeloixtlahuaca</t>
@@ -5066,9 +6731,14 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>San Salvador el Seco</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C355">
@@ -5079,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Santa Isabel Cholula</t>
@@ -5092,6 +6767,11 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>Santo Tomás Hueyotlipan</t>
@@ -5105,9 +6785,14 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Tecali de Herrera</t>
+          <t>Tecali De Herrera</t>
         </is>
       </c>
       <c r="C358">
@@ -5118,6 +6803,11 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Tecomatlán</t>
@@ -5131,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -5144,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -5157,6 +6857,11 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
           <t>Teopantlán</t>
@@ -5170,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -5183,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Tepemaxalco</t>
@@ -5196,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -5209,9 +6929,14 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C366">
@@ -5222,6 +6947,11 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
           <t>Tepeyahualco</t>
@@ -5235,9 +6965,14 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Tepeyahualco de Cuauhtémoc</t>
+          <t>Tepeyahualco De Cuauhtémoc</t>
         </is>
       </c>
       <c r="C368">
@@ -5248,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>Tianguismanalco</t>
@@ -5261,6 +7001,11 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
           <t>Tilapa</t>
@@ -5274,9 +7019,14 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C371">
@@ -5287,6 +7037,11 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -5300,6 +7055,11 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
           <t>Tlanepantla</t>
@@ -5313,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>Tlapanalá</t>
@@ -5326,6 +7091,11 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -5339,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>Tochimilco</t>
@@ -5352,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Tochtepec</t>
@@ -5365,6 +7145,11 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -5378,6 +7163,11 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
           <t>Tzicatlacoyan</t>
@@ -5391,9 +7181,14 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Xayacatlán de Bravo</t>
+          <t>Xayacatlán De Bravo</t>
         </is>
       </c>
       <c r="C380">
@@ -5404,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -5417,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>Xochiltepec</t>
@@ -5430,6 +7235,11 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -5443,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -5456,6 +7271,11 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -5469,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -5482,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -5495,6 +7325,11 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5526,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>Colón</t>
@@ -5539,9 +7379,14 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C391">
@@ -5552,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -5565,9 +7415,14 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C393">
@@ -5578,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5609,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5640,9 +7505,14 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C398">
@@ -5653,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>El Naranjo</t>
@@ -5666,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -5679,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -5692,9 +7577,14 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C402">
@@ -5705,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Villa Juárez</t>
@@ -5718,6 +7613,11 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5749,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -5762,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5793,6 +7703,11 @@
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>Navojoa</t>
@@ -5806,6 +7721,11 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5837,6 +7757,11 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -5850,6 +7775,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>Comalcalco</t>
@@ -5863,6 +7793,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>Cunduacán</t>
@@ -5876,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -5889,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5920,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -5933,6 +7883,11 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -5946,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Llera</t>
@@ -5959,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -5972,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -5985,6 +7955,11 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>Valle Hermoso</t>
@@ -5998,6 +7973,11 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -6011,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6042,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -6055,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -6068,9 +8063,14 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Contla de Juan Cuamatzi</t>
+          <t>Contla De Juan Cuamatzi</t>
         </is>
       </c>
       <c r="C429">
@@ -6081,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -6094,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -6107,9 +8117,14 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Ixtacuixtla de Mariano Matamoros</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C432">
@@ -6120,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>La Magdalena Tlaltelulco</t>
@@ -6133,9 +8153,14 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Mazatecochco de José María Morelos</t>
+          <t>Mazatecochco De José María Morelos</t>
         </is>
       </c>
       <c r="C434">
@@ -6146,9 +8171,14 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Nanacamilpa de Mariano Arista</t>
+          <t>Nanacamilpa De Mariano Arista</t>
         </is>
       </c>
       <c r="C435">
@@ -6159,6 +8189,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
           <t>Natívitas</t>
@@ -6172,9 +8207,14 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Papalotla de Xicohténcatl</t>
+          <t>Papalotla De Xicohténcatl</t>
         </is>
       </c>
       <c r="C437">
@@ -6185,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>San Francisco Tetlanohcan</t>
@@ -6198,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>San Jerónimo Zacualpan</t>
@@ -6211,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>San Juan Huactzinco</t>
@@ -6224,9 +8279,14 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>San Pablo del Monte</t>
+          <t>San Pablo Del Monte</t>
         </is>
       </c>
       <c r="C441">
@@ -6237,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Santa Apolonia Teacalco</t>
@@ -6250,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Santa Catarina Ayometla</t>
@@ -6263,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Teolocholco</t>
@@ -6276,9 +8351,14 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Tepetitla de Lardizábal</t>
+          <t>Tepetitla De Lardizábal</t>
         </is>
       </c>
       <c r="C445">
@@ -6289,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Tepeyanco</t>
@@ -6302,9 +8387,14 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Tetla de la Solidaridad</t>
+          <t>Tetla De La Solidaridad</t>
         </is>
       </c>
       <c r="C447">
@@ -6315,6 +8405,11 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
           <t>Tetlatlahuca</t>
@@ -6328,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -6341,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Totolac</t>
@@ -6354,6 +8459,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
           <t>Tzompantepec</t>
@@ -6367,6 +8477,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Xicohtzinco</t>
@@ -6380,6 +8495,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -6393,6 +8513,11 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6424,6 +8549,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -6437,6 +8567,11 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -6450,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Alvarado</t>
@@ -6463,6 +8603,11 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -6476,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Chicontepec</t>
@@ -6489,6 +8639,11 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -6502,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -6515,6 +8675,11 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
           <t>Gutiérrez Zamora</t>
@@ -6528,6 +8693,11 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -6541,6 +8711,11 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
           <t>Huayacocotla</t>
@@ -6554,9 +8729,14 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C466">
@@ -6567,6 +8747,11 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -6580,9 +8765,14 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Ixhuatlán de Madero</t>
+          <t>Ixhuatlán De Madero</t>
         </is>
       </c>
       <c r="C468">
@@ -6593,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Jáltipan</t>
@@ -6606,6 +8801,11 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -6619,6 +8819,11 @@
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -6632,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Juan Rodríguez Clara</t>
@@ -6645,6 +8855,11 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
           <t>La Antigua</t>
@@ -6658,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -6671,9 +8891,14 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C475">
@@ -6684,6 +8909,11 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -6697,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -6710,6 +8945,11 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Moloacán</t>
@@ -6723,6 +8963,11 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
           <t>Nautla</t>
@@ -6736,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -6749,6 +8999,11 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
           <t>Otatitlán</t>
@@ -6762,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -6775,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Perote</t>
@@ -6788,6 +9053,11 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -6801,6 +9071,11 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Rafael Lucio</t>
@@ -6814,6 +9089,11 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
           <t>Tecolutla</t>
@@ -6827,6 +9107,11 @@
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
           <t>Tempoal</t>
@@ -6840,6 +9125,11 @@
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
           <t>Tenampa</t>
@@ -6853,6 +9143,11 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -6866,6 +9161,11 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -6879,6 +9179,11 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -6892,6 +9197,11 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>Ursulo Galván</t>
@@ -6905,6 +9215,11 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -6918,6 +9233,11 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -6931,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6962,6 +9287,11 @@
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Oxkutzcab</t>
@@ -6975,6 +9305,11 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7006,6 +9341,11 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -7019,6 +9359,11 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7042,41 +9387,6 @@
       </c>
       <c r="D502">
         <v>1</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 497,795</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>Octubre de 2021</t>
-        </is>
       </c>
     </row>
   </sheetData>
